--- a/Outputs/Scenarios/PtX_demand_ES_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_ES_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001803265043043054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01614790245846248</v>
+        <v>0.01785131107648858</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.00359750304517197</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03229580491692496</v>
+        <v>0.02878002436137576</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>2.598199685446796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005382634152820829</v>
+        <v>0.00359750304517197</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002669514355199396</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08703958879574605</v>
+        <v>0.09622121384243575</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.01939107488100511</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1740791775914921</v>
+        <v>0.1551285990480409</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001405007555368104</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02901319626524869</v>
+        <v>0.01939107488100511</v>
       </c>
     </row>
     <row r="43">
